--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487019_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487019_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7554</v>
+        <v>0.5291</v>
       </c>
       <c r="E2" t="n">
-        <v>2.134</v>
+        <v>1.1151</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3786</v>
+        <v>-0.5861</v>
       </c>
       <c r="G2" t="n">
         <v>-2.6327</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5935</v>
+        <v>0.3671</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3016</v>
+        <v>0.2827</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2919</v>
+        <v>0.0844</v>
       </c>
       <c r="V2" t="n">
         <v>1.7679</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9942</v>
+        <v>-0.9373</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1505</v>
+        <v>-0.3672</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8437</v>
+        <v>-0.5702</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.423</v>
+        <v>-0.6458</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3784</v>
+        <v>-0.9117</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0445</v>
+        <v>0.2659</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1577</v>
+        <v>0.0823</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1577</v>
+        <v>0.0034</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2653</v>
+        <v>-0.7281</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2208</v>
+        <v>-0.9151</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0445</v>
+        <v>0.187</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0181</v>
+        <v>-1.1129</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0072</v>
+        <v>-0.4495</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0109</v>
+        <v>-0.6634</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3606</v>
+        <v>-1.6152</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6422</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7184</v>
+        <v>-0.903</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6458</v>
+        <v>-2.423</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9117</v>
+        <v>-1.3784</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2659</v>
+        <v>-1.0445</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0823</v>
+        <v>-1.1577</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0034</v>
+        <v>-1.1577</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7281</v>
+        <v>-1.2653</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9151</v>
+        <v>-0.2208</v>
       </c>
       <c r="O4" t="n">
-        <v>0.187</v>
+        <v>-1.0445</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5362</v>
+        <v>0.3971</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7246</v>
+        <v>0.4455</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8116</v>
+        <v>-0.0484</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3993</v>
+        <v>-1.727</v>
       </c>
       <c r="E5" t="n">
-        <v>0.656</v>
+        <v>0.4468</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0553</v>
+        <v>-2.1739</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5647</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4239</v>
+        <v>-0.7516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0931</v>
+        <v>-0.3023</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3307</v>
+        <v>-0.4493</v>
       </c>
       <c r="V5" t="n">
         <v>0.5893</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2452</v>
+        <v>-1.7997</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2536</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>-0.9917</v>
@@ -922,10 +922,10 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7163</v>
+        <v>-1.2708</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1857</v>
+        <v>-0.7401</v>
       </c>
       <c r="U6" t="n">
         <v>-0.5306</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9308</v>
+        <v>-3.0149</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1935</v>
+        <v>-0.3369</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7373</v>
+        <v>-2.678</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1915</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.423</v>
+        <v>0.3389</v>
       </c>
       <c r="T7" t="n">
-        <v>0.612</v>
+        <v>0.4686</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.189</v>
+        <v>-0.1297</v>
       </c>
       <c r="V7" t="n">
         <v>1.0698</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. MENDES KOVACS</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7604</v>
+        <v>-3.2035</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2414</v>
+        <v>-1.7451</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.519</v>
+        <v>-1.4584</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.013</v>
+        <v>-3.6859</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7527</v>
+        <v>-1.7387</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2602</v>
+        <v>-1.9472</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.327</v>
+        <v>-1.0824</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3664</v>
+        <v>0.2862</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>-1.3686</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.686</v>
+        <v>-2.6034</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3863</v>
+        <v>-2.0249</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2997</v>
+        <v>-0.5786</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0965</v>
+        <v>-1.3657</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1122</v>
+        <v>-0.6627</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2088</v>
+        <v>-0.703</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>K. MENDES KOVACS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0362</v>
+        <v>-3.599</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3999</v>
+        <v>-1.1097</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6363</v>
+        <v>-2.4893</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6859</v>
+        <v>-2.013</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7387</v>
+        <v>-0.7527</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9472</v>
+        <v>-1.2602</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0824</v>
+        <v>-0.327</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2862</v>
+        <v>-0.3664</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3686</v>
+        <v>0.0395</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6034</v>
+        <v>-1.686</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0249</v>
+        <v>-0.3863</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5786</v>
+        <v>-1.2997</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8481</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1983</v>
+        <v>0.0649</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3174</v>
+        <v>0.244</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8809</v>
+        <v>-0.1791</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7964</v>
+        <v>-4.5336</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5387</v>
+        <v>-2.9498</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2577</v>
+        <v>-1.5838</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5683</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2014</v>
+        <v>-0.9386</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2516</v>
+        <v>-0.6627</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0502</v>
+        <v>-0.2759</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0167</v>
+        <v>-5.259</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9556</v>
+        <v>-1.4055</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.061</v>
+        <v>-3.8535</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8772</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9156</v>
+        <v>-0.158</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5465</v>
+        <v>0.0037</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3691</v>
+        <v>-0.1616</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.4658</v>
+        <v>-8.101800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4646</v>
+        <v>-3.1895</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0012</v>
+        <v>-4.9123</v>
       </c>
       <c r="G12" t="n">
         <v>-6.4699</v>
@@ -1390,13 +1390,13 @@
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2546</v>
+        <v>0.1094</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0854</v>
+        <v>0.1897</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1692</v>
+        <v>-0.0803</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3573</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-34.2502</v>
+        <v>-33.2619</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.05</v>
+        <v>-11.062</v>
       </c>
       <c r="F13" t="n">
         <v>-22.2002</v>
@@ -1468,13 +1468,13 @@
         <v>12.3205</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.308199999999999</v>
+        <v>-4.320200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1713</v>
+        <v>-1.1831</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.136900000000001</v>
+        <v>-3.1369</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6981999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.5155</v>
+        <v>10.6367</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9039</v>
+        <v>7.3809</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6115</v>
+        <v>3.2558</v>
       </c>
       <c r="G14" t="n">
         <v>7.374</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9094</v>
+        <v>1.0307</v>
       </c>
       <c r="T14" t="n">
-        <v>0.736</v>
+        <v>0.213</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1734</v>
+        <v>0.8177</v>
       </c>
       <c r="V14" t="n">
         <v>0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6589</v>
+        <v>6.3188</v>
       </c>
       <c r="E15" t="n">
-        <v>3.677</v>
+        <v>3.7816</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9819</v>
+        <v>2.5373</v>
       </c>
       <c r="G15" t="n">
         <v>3.7312</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4821</v>
+        <v>1.1421</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0386</v>
+        <v>0.1432</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4435</v>
+        <v>0.9988</v>
       </c>
       <c r="V15" t="n">
         <v>0.8295</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.366</v>
+        <v>4.9715</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2119</v>
+        <v>2.6232</v>
       </c>
       <c r="F16" t="n">
-        <v>2.154</v>
+        <v>2.3483</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1295</v>
+        <v>4.927</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7194</v>
+        <v>0.0781</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4101</v>
+        <v>4.8489</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1341</v>
+        <v>4.1761</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2137</v>
+        <v>0.0721</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9204</v>
+        <v>4.1041</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9954</v>
+        <v>0.7509</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5057</v>
+        <v>0.006</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4897</v>
+        <v>0.7449</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2098</v>
+        <v>0.7139</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1045</v>
+        <v>0.3486</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1053</v>
+        <v>0.3653</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1786</v>
+        <v>1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8016</v>
+        <v>3.8324</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6818</v>
+        <v>2.2119</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1199</v>
+        <v>1.6205</v>
       </c>
       <c r="G17" t="n">
-        <v>4.927</v>
+        <v>4.1295</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0781</v>
+        <v>1.7194</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8489</v>
+        <v>2.4101</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1761</v>
+        <v>3.1341</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0721</v>
+        <v>1.2137</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1041</v>
+        <v>1.9204</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7509</v>
+        <v>0.9954</v>
       </c>
       <c r="N17" t="n">
-        <v>0.006</v>
+        <v>0.5057</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7449</v>
+        <v>0.4897</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4559</v>
+        <v>0.6762</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5928</v>
+        <v>0.1045</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1369</v>
+        <v>0.5717</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1786</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4986</v>
+        <v>3.4841</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1223</v>
+        <v>2.5354</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3762</v>
+        <v>0.9487</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1433</v>
+        <v>6.015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.467</v>
+        <v>2.8681</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6763</v>
+        <v>3.1469</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1379</v>
+        <v>5.3591</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0195</v>
+        <v>2.3072</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1184</v>
+        <v>3.0519</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0054</v>
+        <v>0.6559</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4475</v>
+        <v>0.5609</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5579</v>
+        <v>0.095</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.1068</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0329</v>
+        <v>0.3788</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5656</v>
+        <v>0.1045</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5327</v>
+        <v>0.2743</v>
       </c>
       <c r="V18" t="n">
-        <v>2.117</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6982</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9802</v>
+        <v>3.3678</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5354</v>
+        <v>1.7039</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4448</v>
+        <v>1.6639</v>
       </c>
       <c r="G19" t="n">
-        <v>6.015</v>
+        <v>1.1433</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8681</v>
+        <v>0.467</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1469</v>
+        <v>0.6763</v>
       </c>
       <c r="J19" t="n">
-        <v>5.3591</v>
+        <v>0.1379</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3072</v>
+        <v>0.0195</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0519</v>
+        <v>0.1184</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6559</v>
+        <v>1.0054</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5609</v>
+        <v>0.4475</v>
       </c>
       <c r="O19" t="n">
-        <v>0.095</v>
+        <v>0.5579</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1068</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1252</v>
+        <v>-0.0978</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1045</v>
+        <v>0.1472</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2297</v>
+        <v>-0.245</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>2.117</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.146</v>
+        <v>2.8905</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4887</v>
+        <v>1.9071</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6573</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>2.0952</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9411</v>
+        <v>-0.1966</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5928</v>
+        <v>-0.1744</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3482</v>
+        <v>-0.0222</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2253</v>
+        <v>0.6622</v>
       </c>
       <c r="E21" t="n">
-        <v>3.0239</v>
+        <v>2.2917</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7986</v>
+        <v>-1.6295</v>
       </c>
       <c r="G21" t="n">
         <v>2.4548</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3331</v>
+        <v>0.77</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5651</v>
+        <v>0.8329</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2319</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3573</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1196</v>
+        <v>-0.1026</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6036</v>
+        <v>-0.6362</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7232</v>
+        <v>0.5336</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6344</v>
+        <v>-0.4207</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8003</v>
+        <v>0.6843</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1659</v>
+        <v>-1.105</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9614</v>
+        <v>0.4522</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0798</v>
+        <v>1.0706</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1184</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.8729</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7204</v>
+        <v>-0.3863</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0475</v>
+        <v>-0.4866</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8214</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2827</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5651</v>
+        <v>0.3757</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2824</v>
+        <v>0.3798</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5893</v>
+        <v>0.5893</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8829</v>
+        <v>-0.2221</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5756</v>
+        <v>-1.2618</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6927</v>
+        <v>1.0396</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5714</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3382</v>
+        <v>0.3225</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1045</v>
+        <v>0.4183</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4427</v>
+        <v>-0.0958</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9395</v>
+        <v>-0.8919</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.473</v>
+        <v>-0.3378</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5336</v>
+        <v>-0.5541</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4207</v>
+        <v>-1.6344</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6843</v>
+        <v>-1.8003</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.105</v>
+        <v>0.1659</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4522</v>
+        <v>-0.9614</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0706</v>
+        <v>-1.0798</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.1184</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8729</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3863</v>
+        <v>-0.7204</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4866</v>
+        <v>0.0475</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0813</v>
+        <v>0.5104</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4611</v>
+        <v>0.6237</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3798</v>
+        <v>-0.1132</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5893</v>
+        <v>-0.5893</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>34.2501</v>
+        <v>34.9474</v>
       </c>
       <c r="E25" t="n">
         <v>22.1999</v>
       </c>
       <c r="F25" t="n">
-        <v>12.0501</v>
+        <v>12.7475</v>
       </c>
       <c r="G25" t="n">
         <v>28.2435</v>
@@ -2386,7 +2386,7 @@
         <v>11.9432</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8231</v>
+        <v>3.823099999999999</v>
       </c>
       <c r="N25" t="n">
         <v>1.715799999999999</v>
@@ -2395,7 +2395,7 @@
         <v>2.1073</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.3204</v>
@@ -2404,16 +2404,16 @@
         <v>12.3206</v>
       </c>
       <c r="S25" t="n">
-        <v>5.3083</v>
+        <v>6.005699999999998</v>
       </c>
       <c r="T25" t="n">
         <v>3.1372</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1713</v>
+        <v>2.8686</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6980999999999999</v>
+        <v>0.6980999999999998</v>
       </c>
       <c r="W25" t="n">
         <v>6.9629</v>
